--- a/artfynd/A 21797-2024 artfynd.xlsx
+++ b/artfynd/A 21797-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4225464</v>
+        <v>88642302</v>
       </c>
       <c r="B2" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90706</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>205306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Sydlig kantmusseron</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tricholoma sejunctum s. str.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Sowerby:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gladvattnet, väst, Öl</t>
+          <t>Mossberga, Öl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598500.2029552712</v>
+        <v>598265</v>
       </c>
       <c r="R2" t="n">
-        <v>6293676.037392584</v>
+        <v>6293705</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2012-07-31</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2012-07-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,33 +768,37 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Torvtäkt, övergiven</t>
+          <t>Ek-hasselskog</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Under hassel</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Åke Rühling</t>
+          <t>Örjan Fritz</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Åke Rühling</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Svampinventeringar i Mittlandet 2018-2021</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6983265</v>
+        <v>2160618</v>
       </c>
       <c r="B3" t="n">
-        <v>107997</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111175</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -828,17 +826,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gladvattnet-Torvmossen, Öl</t>
+          <t>Gladvattnet, syd, Öl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598525.5549271498</v>
+        <v>598522</v>
       </c>
       <c r="R3" t="n">
-        <v>6293672.249610026</v>
+        <v>6293692</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,22 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2013-10-04</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-07-31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2013-10-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-07-31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,33 +879,32 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>sumpskog med torvgravar</t>
+          <t>Torvtäkt, övergiven</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Åke Rühling</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Åke Rühling</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111103250</v>
+        <v>6983265</v>
       </c>
       <c r="B4" t="n">
-        <v>96326</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111175</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,37 +912,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219798</v>
+        <v>219677</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mossberga, Öl</t>
+          <t>Gladvattnet-Torvmossen, Öl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598376.9321684482</v>
+        <v>598526</v>
       </c>
       <c r="R4" t="n">
-        <v>6293616.684583496</v>
+        <v>6293672</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,22 +966,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-07-22</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-10-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-07-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-10-04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,31 +982,35 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>sumpskog med torvgravar</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bård Haugsrud</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bård Haugsrud</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111103330</v>
+        <v>111103250</v>
       </c>
       <c r="B5" t="n">
-        <v>95534</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1037,19 +1018,23 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>224363</v>
+        <v>219798</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1057,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598489.1736476071</v>
+        <v>598377</v>
       </c>
       <c r="R5" t="n">
-        <v>6293677.970098193</v>
+        <v>6293617</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1090,19 +1075,9 @@
           <t>2023-07-22</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-07-22</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,6 +1101,526 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4225462</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Gladvattnet, syd, Öl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>598540</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6293680</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Högsrum</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2012-07-31</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2012-07-31</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Torvtäkt, övergiven</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Åke Rühling</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Åke Rühling</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>4225464</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Gladvattnet, väst, Öl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>598500</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6293676</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Högsrum</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2012-07-31</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2012-07-31</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Torvtäkt, övergiven</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Åke Rühling</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Åke Rühling</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>90095165</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Torvmossen, Öl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>598532</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6293687</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Högsrum</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-01-08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-01-08</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>vallar efter torvbrytning</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson, Ingela Carlström, Thomas Gunnarsson, Tommy Carlström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>90095012</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97985</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Torvmossen, Öl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>598496</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6293654</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Högsrum</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-01-08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-01-08</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>massvis</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>vallar efter torvbrytning</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson, Ingela Carlström, Thomas Gunnarsson, Tommy Carlström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>111103330</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97985</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Mossberga, Öl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>598489</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6293678</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Högsrum</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-07-22</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-07-22</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Bård Haugsrud</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Bård Haugsrud</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21797-2024 artfynd.xlsx
+++ b/artfynd/A 21797-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1423,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>90095012</v>
+        <v>135506730</v>
       </c>
       <c r="B9" t="n">
-        <v>97985</v>
+        <v>98060</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1434,34 +1434,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>224363</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Torvmossen, Öl</t>
+          <t>Mossberga, Öl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>598496</v>
+        <v>598525</v>
       </c>
       <c r="R9" t="n">
-        <v>6293654</v>
+        <v>6293693</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1488,17 +1488,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-01-08</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-01-08</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>massvis</t>
+          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1507,34 +1507,28 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>vallar efter torvbrytning</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Ingela Carlström, Thomas Gunnarsson, Tommy Carlström</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111103330</v>
+        <v>135506731</v>
       </c>
       <c r="B10" t="n">
-        <v>97985</v>
+        <v>98060</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,19 +1536,23 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>224363</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1562,13 +1560,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>598489</v>
+        <v>598475</v>
       </c>
       <c r="R10" t="n">
-        <v>6293678</v>
+        <v>6293691</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1592,12 +1590,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-07-22</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1612,15 +1615,216 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
+          <t>Karl Soler Kinnerbäck</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Karl Soler Kinnerbäck</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>90095012</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97985</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Torvmossen, Öl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>598496</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6293654</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Högsrum</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2021-01-08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2021-01-08</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>massvis</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>vallar efter torvbrytning</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson, Ingela Carlström, Thomas Gunnarsson, Tommy Carlström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>111103330</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97985</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Mossberga, Öl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>598489</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6293678</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Högsrum</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-07-22</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-07-22</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
           <t>Bård Haugsrud</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>Bård Haugsrud</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21797-2024 artfynd.xlsx
+++ b/artfynd/A 21797-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
           <t>Svampinventeringar i Mittlandet 2018-2021</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88642302</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2160618</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1004,6 +1019,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6983265</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1101,6 +1121,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111103250</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4225462</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1311,6 +1341,11 @@
       <c r="AY7" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4225464</t>
         </is>
       </c>
     </row>
@@ -1420,6 +1455,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90095165</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1522,6 +1562,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135506730</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1624,6 +1669,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135506731</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1732,6 +1782,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90095012</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1825,8 +1880,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111103330</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 21797-2024 artfynd.xlsx
+++ b/artfynd/A 21797-2024 artfynd.xlsx
@@ -1466,7 +1466,7 @@
         <v>135506730</v>
       </c>
       <c r="B9" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>135506731</v>
       </c>
       <c r="B10" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 21797-2024 artfynd.xlsx
+++ b/artfynd/A 21797-2024 artfynd.xlsx
@@ -1466,7 +1466,7 @@
         <v>135506730</v>
       </c>
       <c r="B9" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>135506731</v>
       </c>
       <c r="B10" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 21797-2024 artfynd.xlsx
+++ b/artfynd/A 21797-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ10"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1463,10 +1463,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>90095012</v>
+        <v>135506730</v>
       </c>
       <c r="B9" t="n">
-        <v>97985</v>
+        <v>98136</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,34 +1474,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>224363</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Torvmossen, Öl</t>
+          <t>Mossberga, Öl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>598496</v>
+        <v>598525</v>
       </c>
       <c r="R9" t="n">
-        <v>6293654</v>
+        <v>6293693</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1528,17 +1528,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-01-08</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-01-08</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>massvis</t>
+          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1547,39 +1547,33 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>vallar efter torvbrytning</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Ingela Carlström, Thomas Gunnarsson, Tommy Carlström</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/90095012</t>
+          <t>https://artportalen.se/Sighting/135506730</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111103330</v>
+        <v>135506731</v>
       </c>
       <c r="B10" t="n">
-        <v>97985</v>
+        <v>98136</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,19 +1581,23 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>224363</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1607,13 +1605,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>598489</v>
+        <v>598475</v>
       </c>
       <c r="R10" t="n">
-        <v>6293678</v>
+        <v>6293691</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1637,12 +1635,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-07-22</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1657,16 +1660,227 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bård Haugsrud</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bård Haugsrud</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135506731</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>90095012</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97985</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Torvmossen, Öl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>598496</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6293654</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Högsrum</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2021-01-08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2021-01-08</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>massvis</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>vallar efter torvbrytning</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson, Ingela Carlström, Thomas Gunnarsson, Tommy Carlström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90095012</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>111103330</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97985</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Mossberga, Öl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>598489</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6293678</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Högsrum</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-07-22</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-07-22</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Bård Haugsrud</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Bård Haugsrud</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/111103330</t>
         </is>
@@ -1683,6 +1897,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21797-2024 artfynd.xlsx
+++ b/artfynd/A 21797-2024 artfynd.xlsx
@@ -1466,7 +1466,7 @@
         <v>135506730</v>
       </c>
       <c r="B9" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>135506731</v>
       </c>
       <c r="B10" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 21797-2024 artfynd.xlsx
+++ b/artfynd/A 21797-2024 artfynd.xlsx
@@ -1466,7 +1466,7 @@
         <v>135506730</v>
       </c>
       <c r="B9" t="n">
-        <v>98138</v>
+        <v>98155</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>135506731</v>
       </c>
       <c r="B10" t="n">
-        <v>98138</v>
+        <v>98155</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 21797-2024 artfynd.xlsx
+++ b/artfynd/A 21797-2024 artfynd.xlsx
@@ -1466,7 +1466,7 @@
         <v>135506730</v>
       </c>
       <c r="B9" t="n">
-        <v>98155</v>
+        <v>98156</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>135506731</v>
       </c>
       <c r="B10" t="n">
-        <v>98155</v>
+        <v>98156</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
